--- a/AAII_Financials/Quarterly/WFF_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WFF_QTR_FIN.xlsx
@@ -911,10 +911,10 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="E14" s="3">
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>8</v>
@@ -993,10 +993,10 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2600</v>
+        <v>2500</v>
       </c>
       <c r="E17" s="3">
-        <v>2600</v>
+        <v>2500</v>
       </c>
       <c r="F17" s="3">
         <v>1300</v>
@@ -1028,10 +1028,10 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-600</v>
+        <v>-500</v>
       </c>
       <c r="E18" s="3">
-        <v>-600</v>
+        <v>-500</v>
       </c>
       <c r="F18" s="3">
         <v>0</v>
@@ -1113,10 +1113,10 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-500</v>
+        <v>-400</v>
       </c>
       <c r="E21" s="3">
-        <v>-500</v>
+        <v>-400</v>
       </c>
       <c r="F21" s="3">
         <v>0</v>
@@ -1743,10 +1743,10 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F42" s="3">
         <v>200</v>
@@ -1778,10 +1778,10 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>2100</v>
+        <v>1600</v>
       </c>
       <c r="E43" s="3">
-        <v>2100</v>
+        <v>1600</v>
       </c>
       <c r="F43" s="3">
         <v>1800</v>
